--- a/stories/arbres/TREE-LAN-010.xlsx
+++ b/stories/arbres/TREE-LAN-010.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ava est à la cuisine avec maman. Des objets sont sur la table. Maman dit : on compte des objets. Un, deux, trois, quatre, cinq. Ava touche chaque chose. Elle dit le nombre.</t>
+          <t>Ava est à la cuisine avec maman. Des objets sont sur la table. On compte des objets. Un, deux, trois, quatre, cinq. Ava touche chaque chose. Elle dit le nombre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1297,6 +1314,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Ava est à la cuisine avec maman. Des objets sont sur la table.
+maman|On compte des objets.
+narrateur|Un, deux, trois, quatre, cinq. Ava touche chaque chose. Elle dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1483,6 +1507,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la table, l'évier, ou le panier.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1641,6 +1670,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|À la table, Ava compte des objets. Une cuillère. Deux. Trois. Elle dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1817,6 +1851,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|À la table, que fait Ava ?</t>
         </is>
       </c>
     </row>
@@ -1981,6 +2020,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Ava a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2167,6 +2211,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cuillères, les pommes, ou les bols.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2325,6 +2374,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Ava aligne les cuillères. Elle compte des objets. Un, deux, trois.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2511,6 +2565,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2669,6 +2728,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à trois, avec les cuillères, à la table. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2831,6 +2895,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2989,6 +3058,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à cinq, avec les cuillères, à la table. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3151,6 +3225,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3309,6 +3388,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à dix, avec les cuillères, à la table. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3471,6 +3555,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3629,6 +3718,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Les pommes sont rouges. Ava compte des objets. Elle dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3815,6 +3909,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3973,6 +4072,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à trois, avec les pommes, à la table. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4135,6 +4239,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4293,6 +4402,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à cinq, avec les pommes, à la table. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4455,6 +4569,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4613,6 +4732,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à dix, avec les pommes, à la table. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4775,6 +4899,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4933,6 +5062,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Les bols s'empilent. Ava compte des objets. Cinq.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5119,6 +5253,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5277,6 +5416,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à trois, avec les bols, à la table. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5439,6 +5583,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5597,6 +5746,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à cinq, avec les bols, à la table. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5759,6 +5913,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5917,6 +6076,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à dix, avec les bols, à la table. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6079,6 +6243,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6237,6 +6406,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|À l'évier, Ava compte des objets. Un bol. Deux bols. Elle dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6413,6 +6587,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|À l'évier, que fait Ava ?</t>
         </is>
       </c>
     </row>
@@ -6577,6 +6756,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On compte des objets. On dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6765,6 +6949,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cuillères, les pommes, ou les bols.</t>
         </is>
       </c>
     </row>
@@ -6925,6 +7114,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|À l'évier, les cuillères. Ava compte des objets. Le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7111,6 +7305,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7269,6 +7468,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à trois, avec les cuillères, à l'évier. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7431,6 +7635,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7589,6 +7798,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à cinq, avec les cuillères, à l'évier. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7751,6 +7965,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7909,6 +8128,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à dix, avec les cuillères, à l'évier. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8071,6 +8295,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8229,6 +8458,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Des pommes près de l'eau. Ava compte des objets.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8415,6 +8649,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8573,6 +8812,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à trois, avec les pommes, à l'évier. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8735,6 +8979,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8893,6 +9142,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à cinq, avec les pommes, à l'évier. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9055,6 +9309,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9213,6 +9472,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à dix, avec les pommes, à l'évier. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9375,6 +9639,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9533,6 +9802,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Les bols ruissellent. Ava compte des objets. Elle dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9719,6 +9993,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9877,6 +10156,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à trois, avec les bols, à l'évier. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10039,6 +10323,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10197,6 +10486,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à cinq, avec les bols, à l'évier. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10359,6 +10653,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10517,6 +10816,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à dix, avec les bols, à l'évier. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10679,6 +10983,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10837,6 +11146,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le panier, Ava compte des objets. Une pomme. Deux. Trois. Quatre. Cinq. Le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11013,6 +11327,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le panier, que fait Ava ?</t>
         </is>
       </c>
     </row>
@@ -11177,6 +11496,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Ava touche. Elle compte. Elle dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11365,6 +11689,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cuillères, les pommes, ou les bols.</t>
         </is>
       </c>
     </row>
@@ -11525,6 +11854,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le panier, les cuillères. Ava compte des objets.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11711,6 +12045,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11869,6 +12208,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à trois, avec les cuillères, à le panier. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12031,6 +12375,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12189,6 +12538,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à cinq, avec les cuillères, à le panier. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12351,6 +12705,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12509,6 +12868,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à dix, avec les cuillères, à le panier. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12671,6 +13035,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12829,6 +13198,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Les pommes du panier. Ava compte des objets. Dix au plus.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13015,6 +13389,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13173,6 +13552,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à trois, avec les pommes, à le panier. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13335,6 +13719,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13493,6 +13882,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à cinq, avec les pommes, à le panier. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13655,6 +14049,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13813,6 +14212,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à dix, avec les pommes, à le panier. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -13975,6 +14379,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14133,6 +14542,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Les bols du panier. Ava compte des objets. Elle dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14319,6 +14733,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14477,6 +14896,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à trois, avec les bols, à le panier. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14639,6 +15063,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14797,6 +15226,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à cinq, avec les bols, à le panier. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -14959,6 +15393,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15117,6 +15556,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Ava s'arrête à dix, avec les bols, à le panier. Elle a compté des objets. Elle a dit le nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15279,6 +15723,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15297,7 +15746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15321,6 +15770,13 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-LAN-010.xlsx
+++ b/stories/arbres/TREE-LAN-010.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1321,6 +1326,7 @@
 narrateur|Un, deux, trois, quatre, cinq. Ava touche chaque chose. Elle dit le nombre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1512,6 +1518,7 @@
           <t>narrateur|On peut prendre la table, l'évier, ou le panier.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1682,7 @@
           <t>narrateur|À la table, Ava compte des objets. Une cuillère. Deux. Trois. Elle dit le nombre.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1858,6 +1866,7 @@
           <t>narrateur|À la table, que fait Ava ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2025,6 +2034,7 @@
           <t>narrateur|Ava a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2216,6 +2226,7 @@
           <t>narrateur|On peut prendre les cuillères, les pommes, ou les bols.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2379,6 +2390,7 @@
           <t>narrateur|Ava aligne les cuillères. Elle compte des objets. Un, deux, trois.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2570,6 +2582,7 @@
           <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2733,6 +2746,7 @@
           <t>narrateur|Ava s'arrête à trois, avec les cuillères, à la table. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2900,6 +2914,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3063,6 +3078,7 @@
           <t>narrateur|Ava s'arrête à cinq, avec les cuillères, à la table. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3230,6 +3246,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3393,6 +3410,7 @@
           <t>narrateur|Ava s'arrête à dix, avec les cuillères, à la table. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3560,6 +3578,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3723,6 +3742,7 @@
           <t>narrateur|Les pommes sont rouges. Ava compte des objets. Elle dit le nombre.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3914,6 +3934,7 @@
           <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4077,6 +4098,7 @@
           <t>narrateur|Ava s'arrête à trois, avec les pommes, à la table. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4244,6 +4266,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4407,6 +4430,7 @@
           <t>narrateur|Ava s'arrête à cinq, avec les pommes, à la table. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4574,6 +4598,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4737,6 +4762,7 @@
           <t>narrateur|Ava s'arrête à dix, avec les pommes, à la table. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4904,6 +4930,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5067,6 +5094,7 @@
           <t>narrateur|Les bols s'empilent. Ava compte des objets. Cinq.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5258,6 +5286,7 @@
           <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5421,6 +5450,7 @@
           <t>narrateur|Ava s'arrête à trois, avec les bols, à la table. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5588,6 +5618,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5751,6 +5782,7 @@
           <t>narrateur|Ava s'arrête à cinq, avec les bols, à la table. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5918,6 +5950,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6081,6 +6114,7 @@
           <t>narrateur|Ava s'arrête à dix, avec les bols, à la table. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6248,6 +6282,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6411,6 +6446,7 @@
           <t>narrateur|À l'évier, Ava compte des objets. Un bol. Deux bols. Elle dit le nombre.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6594,6 +6630,7 @@
           <t>narrateur|À l'évier, que fait Ava ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6761,6 +6798,7 @@
           <t>narrateur|Oui. On compte des objets. On dit le nombre.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6956,6 +6994,7 @@
           <t>narrateur|On peut prendre les cuillères, les pommes, ou les bols.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7119,6 +7158,7 @@
           <t>narrateur|À l'évier, les cuillères. Ava compte des objets. Le nombre.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7310,6 +7350,7 @@
           <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7473,6 +7514,7 @@
           <t>narrateur|Ava s'arrête à trois, avec les cuillères, à l'évier. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7640,6 +7682,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7803,6 +7846,7 @@
           <t>narrateur|Ava s'arrête à cinq, avec les cuillères, à l'évier. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7970,6 +8014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8133,6 +8178,7 @@
           <t>narrateur|Ava s'arrête à dix, avec les cuillères, à l'évier. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8300,6 +8346,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8463,6 +8510,7 @@
           <t>narrateur|Des pommes près de l'eau. Ava compte des objets.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8654,6 +8702,7 @@
           <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8817,6 +8866,7 @@
           <t>narrateur|Ava s'arrête à trois, avec les pommes, à l'évier. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8984,6 +9034,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9147,6 +9198,7 @@
           <t>narrateur|Ava s'arrête à cinq, avec les pommes, à l'évier. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9314,6 +9366,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9477,6 +9530,7 @@
           <t>narrateur|Ava s'arrête à dix, avec les pommes, à l'évier. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9644,6 +9698,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9807,6 +9862,7 @@
           <t>narrateur|Les bols ruissellent. Ava compte des objets. Elle dit le nombre.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9998,6 +10054,7 @@
           <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10161,6 +10218,7 @@
           <t>narrateur|Ava s'arrête à trois, avec les bols, à l'évier. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10328,6 +10386,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10491,6 +10550,7 @@
           <t>narrateur|Ava s'arrête à cinq, avec les bols, à l'évier. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10658,6 +10718,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10821,6 +10882,7 @@
           <t>narrateur|Ava s'arrête à dix, avec les bols, à l'évier. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10988,6 +11050,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11151,6 +11214,7 @@
           <t>narrateur|Dans le panier, Ava compte des objets. Une pomme. Deux. Trois. Quatre. Cinq. Le nombre.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11334,6 +11398,7 @@
           <t>narrateur|Dans le panier, que fait Ava ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11501,6 +11566,7 @@
           <t>narrateur|Ava touche. Elle compte. Elle dit le nombre.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11696,6 +11762,7 @@
           <t>narrateur|On peut prendre les cuillères, les pommes, ou les bols.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11859,6 +11926,7 @@
           <t>narrateur|Dans le panier, les cuillères. Ava compte des objets.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12050,6 +12118,7 @@
           <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12213,6 +12282,7 @@
           <t>narrateur|Ava s'arrête à trois, avec les cuillères, à le panier. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12380,6 +12450,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12543,6 +12614,7 @@
           <t>narrateur|Ava s'arrête à cinq, avec les cuillères, à le panier. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12710,6 +12782,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12873,6 +12946,7 @@
           <t>narrateur|Ava s'arrête à dix, avec les cuillères, à le panier. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13040,6 +13114,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13203,6 +13278,7 @@
           <t>narrateur|Les pommes du panier. Ava compte des objets. Dix au plus.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13394,6 +13470,7 @@
           <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13557,6 +13634,7 @@
           <t>narrateur|Ava s'arrête à trois, avec les pommes, à le panier. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13724,6 +13802,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13887,6 +13966,7 @@
           <t>narrateur|Ava s'arrête à cinq, avec les pommes, à le panier. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14054,6 +14134,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14217,6 +14298,7 @@
           <t>narrateur|Ava s'arrête à dix, avec les pommes, à le panier. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14384,6 +14466,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14547,6 +14630,7 @@
           <t>narrateur|Les bols du panier. Ava compte des objets. Elle dit le nombre.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14738,6 +14822,7 @@
           <t>narrateur|On peut prendre trois, cinq, ou dix.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14901,6 +14986,7 @@
           <t>narrateur|Ava s'arrête à trois, avec les bols, à le panier. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15068,6 +15154,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15231,6 +15318,7 @@
           <t>narrateur|Ava s'arrête à cinq, avec les bols, à le panier. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15398,6 +15486,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15561,6 +15650,7 @@
           <t>narrateur|Ava s'arrête à dix, avec les bols, à le panier. Elle a compté des objets. Elle a dit le nombre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15728,6 +15818,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15746,7 +15837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15777,6 +15868,20 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15791,7 +15896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15978,6 +16083,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
